--- a/artfynd/A 39961-2025 artfynd.xlsx
+++ b/artfynd/A 39961-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635336</v>
       </c>
       <c r="B2" t="n">
-        <v>79162</v>
+        <v>79166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>128634960</v>
       </c>
       <c r="B3" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>128634985</v>
       </c>
       <c r="B4" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39961-2025 artfynd.xlsx
+++ b/artfynd/A 39961-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635336</v>
       </c>
       <c r="B2" t="n">
-        <v>79166</v>
+        <v>79168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39961-2025 artfynd.xlsx
+++ b/artfynd/A 39961-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635336</v>
       </c>
       <c r="B2" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>128634960</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>128634985</v>
       </c>
       <c r="B4" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39961-2025 artfynd.xlsx
+++ b/artfynd/A 39961-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635336</v>
       </c>
       <c r="B2" t="n">
-        <v>79195</v>
+        <v>79199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39961-2025 artfynd.xlsx
+++ b/artfynd/A 39961-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635336</v>
       </c>
       <c r="B2" t="n">
-        <v>79199</v>
+        <v>79203</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>128634960</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>128634985</v>
       </c>
       <c r="B4" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39961-2025 artfynd.xlsx
+++ b/artfynd/A 39961-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635336</v>
       </c>
       <c r="B2" t="n">
-        <v>79203</v>
+        <v>79108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>128634960</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>128634985</v>
       </c>
       <c r="B4" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39961-2025 artfynd.xlsx
+++ b/artfynd/A 39961-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635336</v>
       </c>
       <c r="B2" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39961-2025 artfynd.xlsx
+++ b/artfynd/A 39961-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635336</v>
       </c>
       <c r="B2" t="n">
-        <v>79113</v>
+        <v>79114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39961-2025 artfynd.xlsx
+++ b/artfynd/A 39961-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635336</v>
       </c>
       <c r="B2" t="n">
-        <v>79114</v>
+        <v>79118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>128634960</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>128634985</v>
       </c>
       <c r="B4" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39961-2025 artfynd.xlsx
+++ b/artfynd/A 39961-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128635336</v>
       </c>
       <c r="B2" t="n">
-        <v>79118</v>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,11 +799,11 @@
         <v>128634960</v>
       </c>
       <c r="B3" t="n">
-        <v>57722</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -920,7 +920,7 @@
         <v>128634985</v>
       </c>
       <c r="B4" t="n">
-        <v>58095</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
